--- a/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T11:56:44+00:00</t>
+    <t>2025-02-18T15:23:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:23:31+00:00</t>
+    <t>2025-02-20T16:18:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T16:18:31+00:00</t>
+    <t>2025-02-20T16:32:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T16:32:32+00:00</t>
+    <t>2025-02-20T17:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T17:12:55+00:00</t>
+    <t>2025-02-24T09:51:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="199">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T09:51:08+00:00</t>
+    <t>2025-02-25T09:09:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,10 +311,6 @@
   </si>
   <si>
     <t>InfrastructureRoot.typeId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
-</t>
   </si>
   <si>
     <t>AssignedEntity.typeId.nullFlavor</t>
@@ -1499,7 +1495,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1507,10 +1503,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1608,39 +1604,39 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K7" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K7" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1691,7 +1687,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1711,39 +1707,39 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K8" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K8" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1794,7 +1790,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1814,39 +1810,39 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K9" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="F9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K9" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1855,49 +1851,49 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="S9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1917,17 +1913,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1945,11 +1941,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2000,7 +1996,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -2020,10 +2016,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2050,7 +2046,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2101,7 +2097,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -2121,10 +2117,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2158,7 +2154,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>74</v>
@@ -2180,7 +2176,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2198,7 +2194,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2218,10 +2214,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2247,7 +2243,7 @@
         <v>95</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -2299,7 +2295,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
@@ -2319,10 +2315,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2420,39 +2416,39 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E15" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K15" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K15" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2503,7 +2499,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -2523,39 +2519,39 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E16" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K16" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K16" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2606,7 +2602,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2626,41 +2622,41 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E17" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K17" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="F17" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G17" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K17" t="s" s="2">
-        <v>112</v>
-      </c>
       <c r="L17" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>133</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2711,7 +2707,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -2731,41 +2727,41 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E18" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="F18" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G18" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K18" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>118</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2816,7 +2812,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -2836,10 +2832,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2862,7 +2858,7 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -2915,7 +2911,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -2935,10 +2931,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2961,10 +2957,10 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>139</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
@@ -2992,11 +2988,11 @@
         <v>74</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>74</v>
@@ -3014,7 +3010,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3034,10 +3030,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3135,10 +3131,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3167,7 +3163,7 @@
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3218,7 +3214,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3238,17 +3234,17 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>80</v>
@@ -3266,11 +3262,11 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3321,7 +3317,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3341,17 +3337,17 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>80</v>
@@ -3369,11 +3365,11 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3424,7 +3420,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3444,17 +3440,17 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>80</v>
@@ -3472,11 +3468,11 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3527,7 +3523,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3547,17 +3543,17 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>80</v>
@@ -3575,11 +3571,11 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3630,7 +3626,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -3650,10 +3646,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3676,11 +3672,11 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3731,7 +3727,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -3751,10 +3747,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3777,11 +3773,11 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3832,7 +3828,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -3852,39 +3848,39 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E29" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="F29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K29" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="F29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G29" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K29" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3935,7 +3931,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -3955,39 +3951,39 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E30" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="F30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K30" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="F30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K30" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4038,7 +4034,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4058,17 +4054,17 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>80</v>
@@ -4086,11 +4082,11 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4141,7 +4137,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4161,10 +4157,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4187,10 +4183,10 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
@@ -4242,7 +4238,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4262,10 +4258,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4288,10 +4284,10 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
@@ -4343,7 +4339,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4363,10 +4359,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4389,10 +4385,10 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
@@ -4444,7 +4440,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4464,10 +4460,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4490,10 +4486,10 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
@@ -4545,7 +4541,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4565,10 +4561,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4591,7 +4587,7 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
@@ -4644,7 +4640,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4664,10 +4660,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4743,7 +4739,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>

--- a/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T09:09:15+00:00</t>
+    <t>2025-03-05T10:03:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>assignedEntity</t>
+    <t>CDA - assignedEntity</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T10:03:58+00:00</t>
+    <t>2025-04-22T14:43:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -944,42 +944,42 @@
   <dimension ref="A1:AK37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.25" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.25" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="24.9375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="37.9375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="37.9375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="21.37890625" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="151.96875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="130.28515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.6640625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.59765625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.20703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.09375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="32.75390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.98046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-22T14:43:59+00:00</t>
+    <t>2025-04-23T09:14:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:14:13+00:00</t>
+    <t>2025-05-19T09:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-19T09:31:54+00:00</t>
+    <t>2025-05-20T13:20:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:20:55+00:00</t>
+    <t>2025-05-23T08:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T08:30:51+00:00</t>
+    <t>2025-05-23T15:44:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T15:44:19+00:00</t>
+    <t>2025-08-01T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T08:11:50+00:00</t>
+    <t>2025-08-22T10:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T10:16:53+00:00</t>
+    <t>2025-08-25T15:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2131,7 +2131,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>

--- a/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:42:10+00:00</t>
+    <t>2025-10-02T14:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T14:05:03+00:00</t>
+    <t>2025-10-02T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T15:16:38+00:00</t>
+    <t>2025-10-13T15:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
